--- a/files/九龙-启德-天玺．海第1期.xlsx
+++ b/files/九龙-启德-天玺．海第1期.xlsx
@@ -3272,23 +3272,19 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>119060000</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>56885</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3297,12 +3293,12 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
@@ -3312,7 +3308,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3408,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -18340,22 +18336,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -18858,37 +18854,37 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>A | 2093呎 (4+房)
+$11906万
+$56,885/呎
+(26年-09月-08日)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 1408呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 2093呎 (4+房)
 招标单位
 -
-(在售)</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="inlineStr">
-        <is>
-          <t>B | 1408呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr"/>
-      <c r="E24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>A | 2093呎 (4+房)
-招标单位
--
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">

--- a/files/九龙-启德-天玺．海第1期.xlsx
+++ b/files/九龙-启德-天玺．海第1期.xlsx
@@ -3408,23 +3408,19 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>116800000</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>55805</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3433,12 +3429,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -3448,7 +3444,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18346,12 +18342,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -18879,12 +18875,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>A | 2093呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$11680万
+$55,805/呎
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">

--- a/files/九龙-启德-天玺．海第1期.xlsx
+++ b/files/九龙-启德-天玺．海第1期.xlsx
@@ -1268,23 +1268,19 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>169533000</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>79073</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1293,12 +1289,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1308,7 +1304,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18332,7 +18328,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18342,7 +18338,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -18475,12 +18471,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>A | 2144呎 (4+房)
-招标单位
--
-(在售)</t>
+$16953万
+$79,073/呎
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">

--- a/files/九龙-启德-天玺．海第1期.xlsx
+++ b/files/九龙-启德-天玺．海第1期.xlsx
@@ -3273,7 +3273,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -18851,7 +18851,7 @@
           <t>A | 2093呎 (4+房)
 $11906万
 $56,885/呎
-(26年-09月-08日)</t>
+(26年-10月-07日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">

--- a/files/九龙-启德-天玺．海第1期.xlsx
+++ b/files/九龙-启德-天玺．海第1期.xlsx
@@ -1273,7 +1273,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -11724,12 +11724,12 @@
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J163" s="3" t="inlineStr">
@@ -11739,12 +11739,12 @@
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L163" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M163" s="3" t="inlineStr">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="N163" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18476,7 +18476,7 @@
           <t>A | 2144呎 (4+房)
 $16953万
 $79,073/呎
-(26年-09月-21日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -18876,7 +18876,7 @@
           <t>A | 2093呎 (4+房)
 $11680万
 $55,805/呎
-(26年-09月-14日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -18988,22 +18988,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -19213,12 +19213,12 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -19453,12 +19453,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -20562,22 +20562,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -20639,12 +20639,12 @@
 (24年-11月-21日)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 1366呎 (4+房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr"/>

--- a/files/九龙-启德-天玺．海第1期.xlsx
+++ b/files/九龙-启德-天玺．海第1期.xlsx
@@ -4438,7 +4438,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4718,23 +4718,19 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>37510000</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>33976</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4743,12 +4739,12 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -4758,7 +4754,7 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5274,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -5288,12 +5284,12 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -5303,12 +5299,12 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -5318,7 +5314,7 @@
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5554,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -5568,12 +5564,12 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
@@ -5583,12 +5579,12 @@
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
@@ -5598,7 +5594,7 @@
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6110,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -6124,12 +6120,12 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
@@ -6139,12 +6135,12 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -6154,7 +6150,7 @@
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6394,23 +6390,19 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>35890000</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>32509</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -6419,12 +6411,12 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
@@ -6434,7 +6426,7 @@
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18988,7 +18980,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -18998,12 +18990,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -19180,12 +19172,12 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -19213,92 +19205,92 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+$3751万
+$33,976/呎
+(26年-10月-20日)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1104呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 541呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 560呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 789呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
 招标单位
 -
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr"/>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
--
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>B | 541呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>C | 560呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>D | 789呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>A | 1104呎 (4+房)
--
--
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -19333,12 +19325,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -19413,12 +19405,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -19453,12 +19445,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>A | 1104呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$3589万
+$32,509/呎
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
